--- a/Selenium Cheatsheets/XPath-CSSSelector Mind Map.xlsx
+++ b/Selenium Cheatsheets/XPath-CSSSelector Mind Map.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/939c1bf4b082bbe3/Desktop/Projects/Testing Projects/Python-Pytest-Robot/Automation-Testing-with-Python/References/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenova\OneDrive\Desktop\TestingDocumentation\Selenium Cheatsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_21C89FCDF21DFB95F0994269EDE04F4AB30EF49B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7A2BE2C-851C-4BBF-A18A-05B904E5E669}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7838A2F-EC67-4A17-A7E1-C549D57272CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="XPath" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">XPath!$A$1:$E$43</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">XPath!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1789,7 +1795,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1804,52 +1810,665 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1860,6 +2479,35 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{31C94654-B4ED-4F68-914B-F2289CDFE2C9}" name="Table1" displayName="Table1" ref="A1:F21" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="17" tableBorderDxfId="18" totalsRowBorderDxfId="16">
+  <autoFilter ref="A1:F21" xr:uid="{31C94654-B4ED-4F68-914B-F2289CDFE2C9}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{AD7FAB0B-1217-44A0-AE0D-821AF4E754B5}" name="Selector Type" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{77C7A32E-7CE7-46C5-AF0B-64523DCF5271}" name="Description" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{E076A1F8-6A9C-48A0-A4CE-2E6709176994}" name="XPath Syntax" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{7FA280D3-BB00-40AE-A4AA-9FF65C114BB5}" name="XPath Example" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{925176F6-45C5-4945-8BCE-819A26932E39}" name="CSS Selector Syntax" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{8C39C7F9-1425-41F8-B4ED-44DF487DE763}" name="CSS Selector Example" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4177BB32-8971-48BE-A87E-B679391DD4C7}" name="Table2" displayName="Table2" ref="A1:E40" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:E40" xr:uid="{4177BB32-8971-48BE-A87E-B679391DD4C7}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{C5C1531F-4C3B-4DD1-8FDF-5E46790FE773}" name="Category" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{E1602D7C-FE3C-40B3-B8E1-075DBC9A2627}" name="Syntax" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{4E2510FA-FBEC-4686-9B33-96BA6384F919}" name="Description" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{BFC810E8-A4ED-486E-8DCD-083D041AE55E}" name="Example" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{D2BF04FB-9A66-4379-94D7-8185B6D0D831}" name="Concept Clear" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2150,986 +2798,1090 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" ht="45">
+      <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="45">
+      <c r="A3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="45">
+      <c r="A4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="60">
+      <c r="A5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="90">
+      <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:6" ht="60">
+      <c r="A7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:6" ht="45">
+      <c r="A8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:6" ht="75">
+      <c r="A9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:6" ht="60">
+      <c r="A10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:6" ht="60">
+      <c r="A11" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:6" ht="60">
+      <c r="A12" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:6" ht="45">
+      <c r="A13" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:6" ht="45">
+      <c r="A14" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="14" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:6" ht="60">
+      <c r="A15" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:6" ht="60">
+      <c r="A16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:6" ht="45">
+      <c r="A17" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:6" ht="60">
+      <c r="A18" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:6" ht="45">
+      <c r="A19" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:6" ht="45">
+      <c r="A20" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:6" ht="60">
+      <c r="A21" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="22" t="s">
         <v>61</v>
       </c>
     </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="6" t="s">
         <v>230</v>
       </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="B25" s="12" t="s">
+      <c r="A25" s="2"/>
+      <c r="B25" s="6" t="s">
         <v>231</v>
       </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="B26" s="12" t="s">
+      <c r="A26" s="2"/>
+      <c r="B26" s="6" t="s">
         <v>232</v>
       </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="B27" s="12" t="s">
+      <c r="A27" s="2"/>
+      <c r="B27" s="6" t="s">
         <v>233</v>
       </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="B24" r:id="rId1" display="https://practice.expandtesting.com/xpath-css-tester" xr:uid="{242F11ED-C77E-4793-8BDD-26278CDC97D7}"/>
     <hyperlink ref="B25" r:id="rId2" display="https://selectors.webdriveruniversity.com/" xr:uid="{DA5D8FD4-4D89-4258-8ECE-E34026656E2D}"/>
     <hyperlink ref="B26" r:id="rId3" display="https://demoqa.com/" xr:uid="{98624A94-AA95-453F-8FE8-23F2209851EC}"/>
     <hyperlink ref="B27" r:id="rId4" display="https://serpapi.com/blog/xpath-selector-cheat-sheet-practical-examples-included/" xr:uid="{FBA1D813-8393-4D2E-8C04-277DD147C552}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId6"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26442553-F444-4F23-A1B8-3E7BEDE365E5}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="72" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="31" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:5" ht="30">
+      <c r="A2" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="26" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="9"/>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:5" ht="30">
+      <c r="A3" s="25"/>
+      <c r="B3" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="11" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="7" t="s">
+      <c r="E3" s="27"/>
+    </row>
+    <row r="4" spans="1:5" ht="30">
+      <c r="A4" s="25"/>
+      <c r="B4" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="7" t="s">
+      <c r="E4" s="27"/>
+    </row>
+    <row r="5" spans="1:5" ht="30">
+      <c r="A5" s="25"/>
+      <c r="B5" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="9"/>
-      <c r="B6" s="7" t="s">
+      <c r="E5" s="27"/>
+    </row>
+    <row r="6" spans="1:5" ht="30">
+      <c r="A6" s="25"/>
+      <c r="B6" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="11" t="s">
         <v>129</v>
       </c>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="11" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="9" t="s">
+      <c r="E7" s="27"/>
+    </row>
+    <row r="8" spans="1:5" ht="30">
+      <c r="A8" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="11" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="9"/>
-      <c r="B9" s="7" t="s">
+      <c r="E8" s="27"/>
+    </row>
+    <row r="9" spans="1:5" ht="30">
+      <c r="A9" s="25"/>
+      <c r="B9" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="11" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="9"/>
-      <c r="B10" s="7" t="s">
+      <c r="E9" s="27"/>
+    </row>
+    <row r="10" spans="1:5" ht="30">
+      <c r="A10" s="25"/>
+      <c r="B10" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="11" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="9"/>
-      <c r="B11" s="7" t="s">
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:5" ht="30">
+      <c r="A11" s="25"/>
+      <c r="B11" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="11" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="9"/>
-      <c r="B12" s="7" t="s">
+      <c r="E11" s="27"/>
+    </row>
+    <row r="12" spans="1:5" ht="30">
+      <c r="A12" s="25"/>
+      <c r="B12" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="11" t="s">
         <v>148</v>
       </c>
+      <c r="E12" s="27"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="7" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="11" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="9"/>
-      <c r="B14" s="7" t="s">
+      <c r="E13" s="27"/>
+    </row>
+    <row r="14" spans="1:5" ht="30">
+      <c r="A14" s="25"/>
+      <c r="B14" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="11" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="9" t="s">
+      <c r="E14" s="27"/>
+    </row>
+    <row r="15" spans="1:5" ht="30">
+      <c r="A15" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="11" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="9"/>
-      <c r="B16" s="7" t="s">
+      <c r="E15" s="27"/>
+    </row>
+    <row r="16" spans="1:5" ht="30">
+      <c r="A16" s="25"/>
+      <c r="B16" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="11" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="9"/>
-      <c r="B17" s="7" t="s">
+      <c r="E16" s="27"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="25"/>
+      <c r="B17" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="11" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="9"/>
-      <c r="B18" s="7" t="s">
+      <c r="E17" s="27"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="25"/>
+      <c r="B18" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="9"/>
-      <c r="B19" s="7" t="s">
+      <c r="E18" s="27"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="25"/>
+      <c r="B19" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="11" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="9"/>
-      <c r="B20" s="7" t="s">
+      <c r="E19" s="27"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="25"/>
+      <c r="B20" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="11" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="9"/>
-      <c r="B21" s="7" t="s">
+      <c r="E20" s="27"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="25"/>
+      <c r="B21" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="11" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="9"/>
-      <c r="B22" s="7" t="s">
+      <c r="E21" s="27"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="25"/>
+      <c r="B22" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="11" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="9" t="s">
+      <c r="E22" s="27"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="11" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="9"/>
-      <c r="B24" s="7" t="s">
+      <c r="E23" s="27"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="25"/>
+      <c r="B24" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="11" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="9"/>
-      <c r="B25" s="7" t="s">
+      <c r="E24" s="27"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="25"/>
+      <c r="B25" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="11" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="9" t="s">
+      <c r="E25" s="27"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="11" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="9"/>
-      <c r="B27" s="7" t="s">
+      <c r="E26" s="27"/>
+    </row>
+    <row r="27" spans="1:5" ht="30">
+      <c r="A27" s="25"/>
+      <c r="B27" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="11" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="9"/>
-      <c r="B28" s="7" t="s">
+      <c r="E27" s="27"/>
+    </row>
+    <row r="28" spans="1:5" ht="30">
+      <c r="A28" s="25"/>
+      <c r="B28" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="11" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="9"/>
-      <c r="B29" s="7" t="s">
+      <c r="E28" s="27"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="25"/>
+      <c r="B29" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="11" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="9"/>
-      <c r="B30" s="7" t="s">
+      <c r="E29" s="27"/>
+    </row>
+    <row r="30" spans="1:5" ht="27.75">
+      <c r="A30" s="25"/>
+      <c r="B30" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="11" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="9"/>
-      <c r="B31" s="7" t="s">
+      <c r="E30" s="27"/>
+    </row>
+    <row r="31" spans="1:5" ht="27.75">
+      <c r="A31" s="25"/>
+      <c r="B31" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="11" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="9"/>
-      <c r="B32" s="7" t="s">
+      <c r="E31" s="27"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="25"/>
+      <c r="B32" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="11" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="9"/>
-      <c r="B33" s="7" t="s">
+      <c r="E32" s="27"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="25"/>
+      <c r="B33" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="11" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="9"/>
-      <c r="B34" s="7" t="s">
+      <c r="E33" s="27"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="25"/>
+      <c r="B34" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="11" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="9"/>
-      <c r="B35" s="7" t="s">
+      <c r="E34" s="27"/>
+    </row>
+    <row r="35" spans="1:5" ht="27.75">
+      <c r="A35" s="25"/>
+      <c r="B35" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="11" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="9"/>
-      <c r="B36" s="7" t="s">
+      <c r="E35" s="27"/>
+    </row>
+    <row r="36" spans="1:5" ht="27.75">
+      <c r="A36" s="25"/>
+      <c r="B36" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="11" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="9" t="s">
+      <c r="E36" s="27"/>
+    </row>
+    <row r="37" spans="1:5" ht="30">
+      <c r="A37" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="10" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="9"/>
-      <c r="B38" s="8" t="s">
+      <c r="E37" s="27"/>
+    </row>
+    <row r="38" spans="1:5" ht="30">
+      <c r="A38" s="25"/>
+      <c r="B38" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="10" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="9"/>
-      <c r="B39" s="8" t="s">
+      <c r="E38" s="27"/>
+    </row>
+    <row r="39" spans="1:5" ht="45">
+      <c r="A39" s="25"/>
+      <c r="B39" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="10" t="s">
         <v>228</v>
       </c>
+      <c r="E39" s="27"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="24"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A14"/>
-    <mergeCell ref="A15:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A36"/>
-    <mergeCell ref="A37:A39"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>